--- a/tests/projectWorkSpaceERP/finance/Project Costing/Change Project Status.xlsx
+++ b/tests/projectWorkSpaceERP/finance/Project Costing/Change Project Status.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="16">
   <si>
     <t>Dataset</t>
   </si>
@@ -40,6 +40,9 @@
     <t>ProjectStatus</t>
   </si>
   <si>
+    <t>CategoryName</t>
+  </si>
+  <si>
     <t>US BU</t>
   </si>
   <si>
@@ -52,10 +55,10 @@
     <t>@+34Ll8I_|ib</t>
   </si>
   <si>
-    <t>XXON CR Pjt Class Categories</t>
-  </si>
-  <si>
-    <t>XXON CR Pjt Cls Code</t>
+    <t>WSP-Global Service Offerings</t>
+  </si>
+  <si>
+    <t>Advisory</t>
   </si>
   <si>
     <t>Active</t>
@@ -66,7 +69,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -84,12 +87,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -121,7 +118,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -141,9 +138,6 @@
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -154,7 +148,7 @@
       <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
+      <alignment horizontal="right"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -461,18 +455,19 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="11" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="9" width="15.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="9" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="9" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="12" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="8" width="15.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="8" width="14.147857142857141" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="8" width="14.147857142857141" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="8" width="14.147857142857141" customWidth="1" bestFit="1"/>
+    <col min="10" max="10" style="11" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="20.25">
@@ -500,100 +495,112 @@
       <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1"/>
+      <c r="I1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="20.25">
       <c r="A2" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E2" s="5">
         <v>380871860776</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I2" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="H2" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I2" s="5"/>
+      <c r="J2" s="5"/>
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="20.25">
       <c r="A3" s="3"/>
       <c r="B3" s="3"/>
       <c r="C3" s="6"/>
       <c r="D3" s="3"/>
-      <c r="E3" s="7"/>
+      <c r="E3" s="5"/>
       <c r="F3" s="3"/>
       <c r="G3" s="3"/>
       <c r="H3" s="3"/>
-      <c r="I3" s="5"/>
+      <c r="I3" s="3"/>
+      <c r="J3" s="5"/>
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="20.25">
       <c r="A4" s="3"/>
       <c r="B4" s="3"/>
       <c r="C4" s="6"/>
       <c r="D4" s="4"/>
-      <c r="E4" s="7"/>
+      <c r="E4" s="5"/>
       <c r="F4" s="3"/>
       <c r="G4" s="3"/>
       <c r="H4" s="3"/>
-      <c r="I4" s="5"/>
+      <c r="I4" s="3"/>
+      <c r="J4" s="5"/>
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="20.25">
-      <c r="A5" s="8"/>
+      <c r="A5" s="7"/>
       <c r="B5" s="3"/>
       <c r="C5" s="6"/>
       <c r="D5" s="3"/>
-      <c r="E5" s="7"/>
+      <c r="E5" s="5"/>
       <c r="F5" s="3"/>
       <c r="G5" s="3"/>
       <c r="H5" s="3"/>
-      <c r="I5" s="5"/>
+      <c r="I5" s="3"/>
+      <c r="J5" s="5"/>
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="20.25">
       <c r="A6" s="3"/>
       <c r="B6" s="3"/>
       <c r="C6" s="6"/>
       <c r="D6" s="3"/>
-      <c r="E6" s="7"/>
+      <c r="E6" s="5"/>
       <c r="F6" s="3"/>
       <c r="G6" s="3"/>
       <c r="H6" s="3"/>
-      <c r="I6" s="5"/>
+      <c r="I6" s="3"/>
+      <c r="J6" s="5"/>
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="20.25">
       <c r="A7" s="3"/>
       <c r="B7" s="3"/>
       <c r="C7" s="6"/>
       <c r="D7" s="3"/>
-      <c r="E7" s="7"/>
+      <c r="E7" s="5"/>
       <c r="F7" s="3"/>
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
-      <c r="I7" s="5"/>
+      <c r="I7" s="3"/>
+      <c r="J7" s="5"/>
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="20.25">
       <c r="A8" s="3"/>
       <c r="B8" s="3"/>
       <c r="C8" s="6"/>
       <c r="D8" s="3"/>
-      <c r="E8" s="7"/>
+      <c r="E8" s="5"/>
       <c r="F8" s="3"/>
       <c r="G8" s="3"/>
       <c r="H8" s="3"/>
-      <c r="I8" s="5"/>
+      <c r="I8" s="3"/>
+      <c r="J8" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
